--- a/data/trans_dic/P2C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,69; 38,33</t>
+          <t>29,71; 38,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,46; 49,02</t>
+          <t>39,26; 48,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,02; 30,87</t>
+          <t>22,05; 30,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 13,89</t>
+          <t>7,95; 13,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,46; 42,14</t>
+          <t>31,25; 42,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 59,71</t>
+          <t>48,2; 60,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,55; 48,15</t>
+          <t>38,14; 48,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 16,97</t>
+          <t>11,18; 16,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,76; 38,6</t>
+          <t>31,67; 38,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,86; 51,6</t>
+          <t>44,52; 51,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 37,31</t>
+          <t>30,14; 37,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,0</t>
+          <t>10,11; 14,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 34,53</t>
+          <t>24,59; 34,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,62; 51,45</t>
+          <t>40,14; 50,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,65; 42,84</t>
+          <t>33,11; 43,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 12,47</t>
+          <t>6,87; 12,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,22; 45,15</t>
+          <t>35,22; 45,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,04; 67,22</t>
+          <t>56,4; 67,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,69; 54,08</t>
+          <t>43,03; 53,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 17,89</t>
+          <t>11,72; 17,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,5; 38,48</t>
+          <t>31,31; 38,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,31; 56,95</t>
+          <t>48,97; 56,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,47; 46,97</t>
+          <t>39,78; 47,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 14,32</t>
+          <t>9,79; 13,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,89; 35,25</t>
+          <t>26,95; 35,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,0; 49,09</t>
+          <t>41,33; 49,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,18; 37,46</t>
+          <t>29,47; 37,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 17,45</t>
+          <t>3,66; 17,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,23; 52,89</t>
+          <t>36,99; 53,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,38; 55,9</t>
+          <t>43,45; 55,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,86; 48,71</t>
+          <t>33,07; 48,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,3</t>
+          <t>9,59; 18,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,93; 37,8</t>
+          <t>30,79; 38,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,2; 50,02</t>
+          <t>43,02; 49,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,69</t>
+          <t>31,5; 38,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,27</t>
+          <t>4,7; 16,17</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 31,93</t>
+          <t>26,61; 31,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,94; 51,51</t>
+          <t>44,89; 51,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 34,26</t>
+          <t>28,9; 34,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 17,19</t>
+          <t>12,81; 17,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,29; 42,36</t>
+          <t>34,78; 42,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,0; 60,54</t>
+          <t>53,13; 60,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,95; 46,8</t>
+          <t>39,82; 46,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 65,28</t>
+          <t>14,77; 59,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,54; 34,91</t>
+          <t>30,59; 35,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,37; 54,23</t>
+          <t>49,41; 54,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,62; 38,93</t>
+          <t>34,56; 38,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 44,74</t>
+          <t>14,71; 48,6</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,96; 34,76</t>
+          <t>24,48; 34,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,98; 48,07</t>
+          <t>39,1; 48,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,38; 37,22</t>
+          <t>29,28; 36,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,94</t>
+          <t>10,01; 15,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,99; 42,34</t>
+          <t>34,38; 41,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,7; 59,86</t>
+          <t>52,12; 59,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,16; 43,99</t>
+          <t>36,83; 44,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 21,36</t>
+          <t>13,23; 21,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,48; 37,66</t>
+          <t>31,79; 37,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,19; 54,19</t>
+          <t>48,44; 53,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,76; 40,15</t>
+          <t>34,44; 39,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,22; 18,34</t>
+          <t>13,34; 18,42</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,44; 22,32</t>
+          <t>13,96; 22,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,38; 36,89</t>
+          <t>26,07; 37,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,76; 27,28</t>
+          <t>17,21; 27,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,5</t>
+          <t>3,57; 13,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,56; 29,63</t>
+          <t>24,36; 29,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,41; 44,43</t>
+          <t>38,64; 44,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,24; 31,72</t>
+          <t>25,72; 31,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 24,79</t>
+          <t>19,35; 24,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,75; 27,44</t>
+          <t>23,05; 27,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,9; 42,26</t>
+          <t>36,93; 42,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,88; 29,83</t>
+          <t>24,87; 29,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,09; 20,66</t>
+          <t>16,27; 20,92</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,52; 30,79</t>
+          <t>27,55; 30,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,25; 46,6</t>
+          <t>43,11; 46,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,7; 32,84</t>
+          <t>29,79; 33,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,24</t>
+          <t>9,21; 13,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,89; 36,1</t>
+          <t>32,97; 36,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,89; 53,26</t>
+          <t>50,01; 53,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,87; 40,48</t>
+          <t>37,05; 40,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,63; 36,22</t>
+          <t>16,65; 36,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,68; 33,01</t>
+          <t>30,81; 33,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47,05; 49,47</t>
+          <t>47,02; 49,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,91; 36,26</t>
+          <t>33,92; 36,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,0; 25,02</t>
+          <t>14,0; 25,72</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>140673; 181613</t>
+          <t>140777; 180975</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>168158; 214332</t>
+          <t>171636; 213737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94469; 132442</t>
+          <t>94632; 132765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40436; 70170</t>
+          <t>40160; 69078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96480; 129250</t>
+          <t>95830; 130077</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>150381; 187766</t>
+          <t>151580; 188901</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>130314; 167105</t>
+          <t>132369; 168329</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50936; 75914</t>
+          <t>50039; 75496</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>247850; 301283</t>
+          <t>247181; 301067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>329716; 387859</t>
+          <t>334642; 390319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>235630; 289601</t>
+          <t>233957; 290261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95669; 133355</t>
+          <t>96302; 134239</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89873; 126717</t>
+          <t>90216; 125081</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>170131; 215465</t>
+          <t>168124; 213333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123153; 161608</t>
+          <t>124901; 165475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31835; 56409</t>
+          <t>31075; 56732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>130983; 167912</t>
+          <t>130958; 169327</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>189413; 227207</t>
+          <t>190647; 228407</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>162632; 201312</t>
+          <t>160173; 200417</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44854; 68426</t>
+          <t>44829; 67695</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>232748; 284297</t>
+          <t>231305; 284448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>373204; 430965</t>
+          <t>370588; 431150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>295790; 352012</t>
+          <t>298123; 353418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83396; 119536</t>
+          <t>81713; 115357</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>145832; 191175</t>
+          <t>146197; 191040</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>258087; 308960</t>
+          <t>260148; 309055</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152296; 195529</t>
+          <t>153798; 196259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25218; 116634</t>
+          <t>24433; 115710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>64146; 88744</t>
+          <t>62059; 89264</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>112840; 145407</t>
+          <t>113016; 144329</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54589; 80925</t>
+          <t>54940; 80213</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15582; 28872</t>
+          <t>16015; 30125</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>219641; 268467</t>
+          <t>218690; 270673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>384297; 444936</t>
+          <t>382683; 442310</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>214341; 266221</t>
+          <t>216708; 264855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38363; 135876</t>
+          <t>39236; 135006</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>332326; 395448</t>
+          <t>329540; 395066</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>520805; 596972</t>
+          <t>520253; 594426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>327232; 393825</t>
+          <t>332299; 395241</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>132039; 177847</t>
+          <t>132599; 180782</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>252060; 302601</t>
+          <t>248464; 302575</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>406357; 464142</t>
+          <t>407288; 464595</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>329915; 386526</t>
+          <t>328882; 386072</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>143221; 638521</t>
+          <t>144443; 582607</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>596427; 681636</t>
+          <t>597340; 683598</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>950788; 1044236</t>
+          <t>951408; 1041032</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>683929; 769002</t>
+          <t>682680; 768432</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>293923; 900493</t>
+          <t>296101; 978247</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87498; 121843</t>
+          <t>85821; 120839</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199007; 245465</t>
+          <t>199635; 246559</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182394; 231024</t>
+          <t>181760; 228662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46593; 75742</t>
+          <t>47545; 75657</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>193311; 240826</t>
+          <t>195564; 238784</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>401314; 455851</t>
+          <t>396902; 455426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>274295; 324720</t>
+          <t>271884; 329628</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115369; 179737</t>
+          <t>111290; 178972</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>289400; 346197</t>
+          <t>292203; 348119</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>613047; 689365</t>
+          <t>616200; 683814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>472378; 545592</t>
+          <t>468051; 538984</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>173968; 241452</t>
+          <t>175668; 242517</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40069; 66566</t>
+          <t>41633; 67672</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>70398; 98450</t>
+          <t>69585; 100389</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48136; 78339</t>
+          <t>49419; 78467</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8471; 30073</t>
+          <t>8596; 32131</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>306756; 369973</t>
+          <t>304259; 367840</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>426132; 492887</t>
+          <t>428624; 492600</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>283903; 343176</t>
+          <t>278291; 343050</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>149612; 188716</t>
+          <t>147312; 187978</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>351974; 424439</t>
+          <t>356569; 426117</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>507822; 581628</t>
+          <t>508211; 583243</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>340636; 408454</t>
+          <t>340480; 409145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>161185; 206970</t>
+          <t>162986; 209543</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>899968; 1006928</t>
+          <t>900843; 1009402</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1480051; 1594496</t>
+          <t>1475231; 1597576</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1005686; 1111754</t>
+          <t>1008464; 1119660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>305641; 447149</t>
+          <t>310855; 447554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1111182; 1219543</t>
+          <t>1113919; 1222996</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1771192; 1890883</t>
+          <t>1775396; 1897766</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1302001; 1429607</t>
+          <t>1308397; 1426190</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>594811; 1295902</t>
+          <t>595772; 1304601</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2039989; 2194806</t>
+          <t>2048498; 2200022</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3280019; 3449163</t>
+          <t>3278389; 3453671</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2345902; 2508417</t>
+          <t>2346160; 2506766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>973764; 1739777</t>
+          <t>973280; 1788773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,71; 38,2</t>
+          <t>29,87; 38,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,26; 48,89</t>
+          <t>38,62; 48,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,05; 30,94</t>
+          <t>22,17; 31,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,67</t>
+          <t>8,33; 14,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,25; 42,41</t>
+          <t>31,18; 42,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,2; 60,07</t>
+          <t>47,93; 60,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,14; 48,5</t>
+          <t>37,8; 48,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,87</t>
+          <t>11,1; 16,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,67; 38,58</t>
+          <t>31,42; 38,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,52; 51,93</t>
+          <t>44,67; 52,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,14; 37,4</t>
+          <t>30,08; 37,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 14,09</t>
+          <t>10,59; 14,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,59; 34,09</t>
+          <t>24,86; 34,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,14; 50,94</t>
+          <t>40,35; 51,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,11; 43,87</t>
+          <t>32,71; 43,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,55</t>
+          <t>7,37; 13,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,22; 45,53</t>
+          <t>35,45; 45,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,4; 67,57</t>
+          <t>56,18; 67,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,03; 53,84</t>
+          <t>43,47; 53,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 17,69</t>
+          <t>12,14; 18,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,31; 38,5</t>
+          <t>31,24; 38,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,97; 56,97</t>
+          <t>49,12; 56,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,78; 47,15</t>
+          <t>39,47; 47,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,82</t>
+          <t>10,41; 14,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,95; 35,22</t>
+          <t>26,9; 35,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,33; 49,1</t>
+          <t>41,37; 49,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,47; 37,6</t>
+          <t>29,48; 37,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 17,31</t>
+          <t>13,97; 21,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,99; 53,2</t>
+          <t>37,34; 51,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,45; 55,48</t>
+          <t>42,42; 55,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,07; 48,29</t>
+          <t>32,73; 48,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,05</t>
+          <t>9,54; 17,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,79; 38,11</t>
+          <t>30,95; 37,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,02; 49,72</t>
+          <t>43,27; 50,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,5; 38,49</t>
+          <t>31,31; 38,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 16,17</t>
+          <t>13,42; 19,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 31,9</t>
+          <t>26,71; 32,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,89; 51,29</t>
+          <t>45,21; 51,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 34,38</t>
+          <t>29,21; 34,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 17,47</t>
+          <t>13,99; 18,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 42,36</t>
+          <t>34,75; 42,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,13; 60,6</t>
+          <t>53,45; 61,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 46,75</t>
+          <t>39,81; 47,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 59,57</t>
+          <t>13,49; 17,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,59; 35,01</t>
+          <t>30,34; 34,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,41; 54,06</t>
+          <t>49,41; 53,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,56; 38,9</t>
+          <t>34,29; 38,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,71; 48,6</t>
+          <t>14,4; 17,61</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,48; 34,47</t>
+          <t>24,38; 34,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,1; 48,29</t>
+          <t>38,86; 47,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 36,84</t>
+          <t>29,31; 37,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,93</t>
+          <t>9,47; 14,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,38; 41,98</t>
+          <t>33,7; 41,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,12; 59,8</t>
+          <t>52,36; 59,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,83; 44,65</t>
+          <t>37,34; 44,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 21,27</t>
+          <t>19,16; 23,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,79; 37,87</t>
+          <t>31,19; 37,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,44; 53,75</t>
+          <t>48,03; 53,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,44; 39,66</t>
+          <t>34,73; 39,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 18,42</t>
+          <t>15,93; 19,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 22,69</t>
+          <t>13,54; 22,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,07; 37,62</t>
+          <t>26,05; 36,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,21; 27,33</t>
+          <t>17,46; 27,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 13,36</t>
+          <t>5,23; 16,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,36; 29,46</t>
+          <t>24,57; 29,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,64; 44,4</t>
+          <t>38,41; 44,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,72; 31,7</t>
+          <t>26,1; 31,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,35; 24,69</t>
+          <t>20,26; 25,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,05; 27,55</t>
+          <t>23,17; 27,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,93; 42,38</t>
+          <t>37,17; 42,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,87; 29,88</t>
+          <t>24,99; 29,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 20,92</t>
+          <t>17,43; 22,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,55; 30,87</t>
+          <t>27,68; 30,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,11; 46,69</t>
+          <t>43,1; 46,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,79; 33,07</t>
+          <t>29,77; 33,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,26</t>
+          <t>12,23; 14,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,97; 36,2</t>
+          <t>32,94; 36,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,01; 53,46</t>
+          <t>49,84; 53,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,05; 40,38</t>
+          <t>37,18; 40,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 36,46</t>
+          <t>16,92; 19,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,81; 33,09</t>
+          <t>30,81; 32,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47,02; 49,54</t>
+          <t>46,99; 49,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,24</t>
+          <t>33,92; 36,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,0; 25,72</t>
+          <t>15,04; 16,7</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53166</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60783</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>113949</t>
+          <t>128014</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>140777; 180975</t>
+          <t>141516; 183673</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>171636; 213737</t>
+          <t>168848; 213208</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94632; 132765</t>
+          <t>95142; 133400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40160; 69078</t>
+          <t>45869; 78482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95830; 130077</t>
+          <t>95620; 129172</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151580; 188901</t>
+          <t>150728; 189078</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>132369; 168329</t>
+          <t>131190; 168265</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50039; 75496</t>
+          <t>54203; 81370</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>247181; 301067</t>
+          <t>245226; 302245</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>334642; 390319</t>
+          <t>335767; 392860</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>233957; 290261</t>
+          <t>233433; 288320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96302; 134239</t>
+          <t>110057; 150423</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56077</t>
+          <t>63135</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98801</t>
+          <t>111854</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90216; 125081</t>
+          <t>91211; 126111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>168124; 213333</t>
+          <t>168998; 215326</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124901; 165475</t>
+          <t>123401; 163915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31075; 56732</t>
+          <t>35599; 64881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>130958; 169327</t>
+          <t>131809; 168994</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190647; 228407</t>
+          <t>189889; 227831</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>160173; 200417</t>
+          <t>161815; 199421</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44829; 67695</t>
+          <t>51378; 77254</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>231305; 284448</t>
+          <t>230812; 285151</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>370588; 431150</t>
+          <t>371763; 430261</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>298123; 353418</t>
+          <t>295834; 352446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81713; 115357</t>
+          <t>94345; 131390</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>81332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>105537</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>146197; 191040</t>
+          <t>145898; 190954</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>260148; 309055</t>
+          <t>260388; 311383</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153798; 196259</t>
+          <t>153878; 195177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24433; 115710</t>
+          <t>65882; 100368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62059; 89264</t>
+          <t>62645; 87201</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>113016; 144329</t>
+          <t>110349; 144522</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54940; 80213</t>
+          <t>54373; 80035</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16015; 30125</t>
+          <t>17885; 32411</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>218690; 270673</t>
+          <t>219825; 269505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>382683; 442310</t>
+          <t>384873; 450745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>216708; 264855</t>
+          <t>215440; 267322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39236; 135006</t>
+          <t>88426; 125922</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155024</t>
+          <t>181349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>324167</t>
+          <t>135029</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>479191</t>
+          <t>316379</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>329540; 395066</t>
+          <t>330707; 396502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>520253; 594426</t>
+          <t>523997; 597273</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>332299; 395241</t>
+          <t>335852; 397746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>132599; 180782</t>
+          <t>158328; 208218</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>248464; 302575</t>
+          <t>248232; 300908</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>407288; 464595</t>
+          <t>409811; 468236</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>328882; 386072</t>
+          <t>328777; 388213</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>144443; 582607</t>
+          <t>116177; 153976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>597340; 683598</t>
+          <t>592330; 673785</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>951408; 1041032</t>
+          <t>951497; 1038259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>682680; 768432</t>
+          <t>677401; 763933</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>296101; 978247</t>
+          <t>286969; 350910</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>152533</t>
+          <t>178341</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>213086</t>
+          <t>246843</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85821; 120839</t>
+          <t>85470; 120971</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199635; 246559</t>
+          <t>198398; 244044</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181760; 228662</t>
+          <t>181956; 231695</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47545; 75657</t>
+          <t>53802; 84185</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>195564; 238784</t>
+          <t>191660; 238822</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>396902; 455426</t>
+          <t>398709; 453186</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>271884; 329628</t>
+          <t>275634; 330426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>111290; 178972</t>
+          <t>159193; 199039</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>292203; 348119</t>
+          <t>286692; 347085</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>616200; 683814</t>
+          <t>610976; 684668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>468051; 538984</t>
+          <t>471898; 542849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>175668; 242517</t>
+          <t>222799; 273003</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>167729</t>
+          <t>191707</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>184010</t>
+          <t>214224</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41633; 67672</t>
+          <t>40362; 66235</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69585; 100389</t>
+          <t>69531; 97720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49419; 78467</t>
+          <t>50133; 78996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8596; 32131</t>
+          <t>12413; 38080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>304259; 367840</t>
+          <t>306874; 369784</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>428624; 492600</t>
+          <t>426146; 492773</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>278291; 343050</t>
+          <t>282439; 343668</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>147312; 187978</t>
+          <t>171020; 214539</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>356569; 426117</t>
+          <t>358463; 424123</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>508211; 583243</t>
+          <t>511606; 583668</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>340480; 409145</t>
+          <t>342213; 406125</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>162986; 209543</t>
+          <t>188537; 240136</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>396800</t>
+          <t>463149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>783411</t>
+          <t>659701</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1180211</t>
+          <t>1122851</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>900843; 1009402</t>
+          <t>905133; 1007832</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1475231; 1597576</t>
+          <t>1474755; 1591917</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1008464; 1119660</t>
+          <t>1007889; 1117894</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>310855; 447554</t>
+          <t>420949; 506225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1113919; 1222996</t>
+          <t>1112873; 1223247</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1775396; 1897766</t>
+          <t>1769519; 1891081</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1308397; 1426190</t>
+          <t>1313048; 1431865</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>595772; 1304601</t>
+          <t>615254; 699844</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2048498; 2200022</t>
+          <t>2048305; 2193533</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3278389; 3453671</t>
+          <t>3276407; 3451505</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2346160; 2506766</t>
+          <t>2346467; 2505460</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>973280; 1788773</t>
+          <t>1064310; 1182202</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
